--- a/AtchisonRegime/Outputs/China/df_regSummary_China.xlsx
+++ b/AtchisonRegime/Outputs/China/df_regSummary_China.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>1.327193407704851</v>
+        <v>1.344776664734815</v>
       </c>
       <c r="H2" t="n">
-        <v>5.108640939288379</v>
+        <v>5.001851258233686</v>
       </c>
       <c r="I2" t="n">
         <v>-6.49330771413728</v>
@@ -545,22 +545,22 @@
         <v>12.1040808797468</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06413643788220764</v>
+        <v>0.06832888335471712</v>
       </c>
       <c r="O2" t="n">
         <v>-0.06711984032740836</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1864685281693315</v>
+        <v>0.2074307555318788</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>23.8494781687939</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>21.1810668982901</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>8.65395055376516</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3840496030387139</v>
+        <v>0.2351237710555614</v>
       </c>
       <c r="H6" t="n">
-        <v>3.401990645089062</v>
+        <v>3.412591696523912</v>
       </c>
       <c r="I6" t="n">
         <v>-3.79110563625414</v>
@@ -777,19 +777,19 @@
         <v>10.2113173457014</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L6" t="n">
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01821100348290232</v>
+        <v>0.01168289274284049</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0529738859666341</v>
+        <v>-0.05511394832336292</v>
       </c>
       <c r="P6" t="n">
         <v>0.141968811866646</v>
@@ -835,7 +835,7 @@
         <v>8.779535078076917</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
@@ -893,7 +893,7 @@
         <v>7.257145141894861</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>6.042936784522324</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6880661859561092</v>
+        <v>0.6552474316875557</v>
       </c>
       <c r="H10" t="n">
-        <v>3.879511980592399</v>
+        <v>3.801372264025864</v>
       </c>
       <c r="I10" t="n">
         <v>-4.51216419039352</v>
@@ -1009,19 +1009,19 @@
         <v>8.772867259703339</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03295657691296942</v>
+        <v>0.03270904923642388</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06524666334535389</v>
+        <v>-0.06648430172808162</v>
       </c>
       <c r="P10" t="n">
         <v>0.1563695383719861</v>
@@ -1067,7 +1067,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
@@ -1125,7 +1125,7 @@
         <v>12.9481215237874</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -1183,7 +1183,7 @@
         <v>7.437988740612401</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
